--- a/backend/downloads/미분양주택현황보고_시·군·구별 미분양현황 (200012 ~ 202508).xlsx
+++ b/backend/downloads/미분양주택현황보고_시·군·구별 미분양현황 (200012 ~ 202508).xlsx
@@ -148,7 +148,7 @@
     <row r="2" customHeight="true" ht="25.0">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-14   10:06</t>
+          <t>다운로드 시간 : 2025-10-14   23:58</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">

--- a/backend/downloads/미분양주택현황보고_시·군·구별 미분양현황 (200012 ~ 202508).xlsx
+++ b/backend/downloads/미분양주택현황보고_시·군·구별 미분양현황 (200012 ~ 202508).xlsx
@@ -151,7 +151,7 @@
     <row r="2" customHeight="true" ht="25.0">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-15   10:05</t>
+          <t>다운로드 시간 : 2025-10-17   03:01</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
